--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121085549</v>
+        <v>121085591</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>90717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590751</v>
+        <v>590755</v>
       </c>
       <c r="R2" t="n">
-        <v>6545026</v>
+        <v>6545059</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121085591</v>
+        <v>121085549</v>
       </c>
       <c r="B3" t="n">
-        <v>90707</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,30 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590755</v>
+        <v>590751</v>
       </c>
       <c r="R3" t="n">
-        <v>6545059</v>
+        <v>6545026</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121085591</v>
+        <v>121085549</v>
       </c>
       <c r="B2" t="n">
-        <v>90717</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590755</v>
+        <v>590751</v>
       </c>
       <c r="R2" t="n">
-        <v>6545059</v>
+        <v>6545026</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121085549</v>
+        <v>121085591</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>90717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +799,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590751</v>
+        <v>590755</v>
       </c>
       <c r="R3" t="n">
-        <v>6545026</v>
+        <v>6545059</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121085549</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121085591</v>
       </c>
       <c r="B3" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121085549</v>
+        <v>121085591</v>
       </c>
       <c r="B2" t="n">
-        <v>100360</v>
+        <v>90730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590751</v>
+        <v>590755</v>
       </c>
       <c r="R2" t="n">
-        <v>6545026</v>
+        <v>6545059</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121085591</v>
+        <v>121085549</v>
       </c>
       <c r="B3" t="n">
-        <v>90729</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,30 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590755</v>
+        <v>590751</v>
       </c>
       <c r="R3" t="n">
-        <v>6545059</v>
+        <v>6545026</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121085591</v>
+        <v>129331081</v>
       </c>
       <c r="B2" t="n">
-        <v>90730</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>3086</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Udden 600m N, Srm</t>
+          <t>Udden 500m N, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590755</v>
+        <v>590848</v>
       </c>
       <c r="R2" t="n">
-        <v>6545059</v>
+        <v>6544947</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,9 +761,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Virkestrave</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -779,50 +774,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121085549</v>
+        <v>121085591</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590751</v>
+        <v>590755</v>
       </c>
       <c r="R3" t="n">
-        <v>6545026</v>
+        <v>6545059</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,6 +884,220 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133305894</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111181</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221037</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vildkaprifol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lonicera periclymenum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Udden 500m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590848</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544947</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121085549</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Udden 600m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590751</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6545026</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129331081</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121085591</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133305894</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,8 +1118,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121085549</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,6 +1121,108 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121085549</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136216371</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99572</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flen, ombyggnad v 55 Prästgårdsskogen mm, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>590788</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6545184</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136216371</t>
         </is>
       </c>
     </row>
@@ -1130,6 +1232,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
